--- a/output/pdf_financials_xlsx/EMO.xlsx
+++ b/output/pdf_financials_xlsx/EMO.xlsx
@@ -5301,46 +5301,46 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.013089</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.013089</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.019904</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.171799</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.425336</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.22795</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.951105</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.059905</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>6.836167</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.837453</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.567628</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.567188</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>7.027701</v>
       </c>
     </row>
     <row r="93">
@@ -8919,7 +8919,11 @@
           <t>Warrant reserve 13</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10208,7 +10212,11 @@
           <t>Warrant reserve 11</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -11181,7 +11189,11 @@
           <t>Warrant reserve 9</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -12077,7 +12089,11 @@
           <t>Warrant reserve 7</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -12700,7 +12716,11 @@
           <t>Warrants reserve 6</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -13499,7 +13519,11 @@
           <t>Warrant reserve 7</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -14223,7 +14247,11 @@
           <t>Warrant reserve 6</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -15228,7 +15256,11 @@
           <t>Warrants reserve 4</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -46737,7 +46769,7 @@
         <v>-0.097623</v>
       </c>
       <c r="G438" s="5" t="n">
-        <v>0.088991</v>
+        <v>-0.088991</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/EMO.xlsx
+++ b/output/pdf_financials_xlsx/EMO.xlsx
@@ -978,40 +978,40 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.022294</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.00637</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>3.9e-05</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>9.8e-05</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000423</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.003464</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000781</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.010267</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.170179</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.376559</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.139508</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.2992</v>
       </c>
     </row>
     <row r="13">
@@ -1834,40 +1834,40 @@
         <v>0.08995</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.033059</v>
+        <v>-2.055353</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.730024</v>
+        <v>-1.736394</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.38639</v>
+        <v>-2.386429</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.520994</v>
+        <v>-1.521092</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.522973</v>
+        <v>-2.523396</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.087441</v>
+        <v>-2.090905</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.087441</v>
+        <v>-2.088222</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-17.23103</v>
+        <v>-17.241297</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-20.705766</v>
+        <v>-20.875945</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-21.493816</v>
+        <v>-21.870375</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.546881</v>
+        <v>-3.686389</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-12.5069</v>
+        <v>-12.8061</v>
       </c>
     </row>
     <row r="28">
@@ -1938,40 +1938,40 @@
         <v>0.08995</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.033059</v>
+        <v>-2.055353</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.730024</v>
+        <v>-1.736394</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.38639</v>
+        <v>-2.386429</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.520994</v>
+        <v>-1.521092</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.522973</v>
+        <v>-2.523396</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.087441</v>
+        <v>-2.090905</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.087441</v>
+        <v>-2.088222</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-17.23103</v>
+        <v>-17.241297</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-20.705766</v>
+        <v>-20.875945</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-21.493816</v>
+        <v>-21.870375</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.546881</v>
+        <v>-3.686389</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-12.5069</v>
+        <v>-12.8061</v>
       </c>
     </row>
     <row r="30">
@@ -2204,13 +2204,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.265011</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.022563</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1.712915</v>
@@ -2219,19 +2219,19 @@
         <v>1.024697</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.050477</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.306773</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.518719</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.031325</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.069783</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>26.77743</v>
@@ -2308,13 +2308,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.265011</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.022563</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1.712915</v>
@@ -2323,19 +2323,19 @@
         <v>1.024697</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.050477</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.306773</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.518719</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.031325</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.069783</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>26.77743</v>
@@ -2932,13 +2932,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.265011</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.035061</v>
+        <v>0.012498</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.010158</v>
@@ -2947,19 +2947,19 @@
         <v>0.107624</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.056076</v>
+        <v>0.005599</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.359856</v>
+        <v>0.053083</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.547631</v>
+        <v>0.028912</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.049204</v>
+        <v>0.017879</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.178965</v>
+        <v>0.109182</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.149858</v>
@@ -8128,7 +8128,11 @@
           <t>Reclamation deposits 10</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -9852,7 +9856,11 @@
           <t>Reclamation deposits 9</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -10487,7 +10495,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -10649,7 +10657,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -14528,7 +14540,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
@@ -17392,7 +17404,11 @@
           <t>(Refund)/payment of reclamation deposits 10</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -19164,7 +19180,11 @@
           <t>Refund of reclamation deposits 10</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -19874,7 +19894,11 @@
           <t>Decrease/(increase) in reclamation deposits 9</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -20495,7 +20519,11 @@
           <t>Increase in reclamation deposits</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -29909,7 +29937,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -33764,7 +33796,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -33857,7 +33889,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -38942,7 +38974,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -40109,7 +40141,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">

--- a/output/pdf_financials_xlsx/EMO.xlsx
+++ b/output/pdf_financials_xlsx/EMO.xlsx
@@ -715,43 +715,43 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.0025</v>
+        <v>0.003446</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.551511</v>
+        <v>0.603015</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.709634</v>
+        <v>0.815774</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.611965</v>
+        <v>0.690773</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.595784</v>
+        <v>0.6197820000000001</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.947479</v>
+        <v>1.033278</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.035572</v>
+        <v>1.123494</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.791364</v>
+        <v>0.887507</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.900406</v>
+        <v>1.997779</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.432574</v>
+        <v>1.581578</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>2.025577</v>
+        <v>2.16717</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>2.916121</v>
+        <v>3.053641</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>2.627085</v>
+        <v>2.793762</v>
       </c>
     </row>
     <row r="8">
@@ -871,43 +871,43 @@
         <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.0025</v>
+        <v>0.003446</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.551511</v>
+        <v>0.603015</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.709634</v>
+        <v>0.815774</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.611965</v>
+        <v>0.690773</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.595784</v>
+        <v>0.6197820000000001</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.947479</v>
+        <v>1.033278</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.035572</v>
+        <v>1.123494</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.791364</v>
+        <v>0.887507</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.900406</v>
+        <v>1.997779</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.432574</v>
+        <v>1.581578</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>2.025577</v>
+        <v>2.16717</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>2.916121</v>
+        <v>3.053641</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>2.627085</v>
+        <v>2.793762</v>
       </c>
     </row>
     <row r="11">
@@ -926,31 +926,31 @@
         <v>-0.11005</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.551511</v>
+        <v>-0.603015</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.709634</v>
+        <v>-0.815774</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.611965</v>
+        <v>-0.690773</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.595784</v>
+        <v>-0.6197820000000001</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.947479</v>
+        <v>-1.033278</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-1.035572</v>
+        <v>-1.123494</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.791364</v>
+        <v>-0.887507</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-1.900406</v>
+        <v>-1.997779</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-1.432574</v>
+        <v>-1.581578</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>-21.930429</v>
@@ -1216,7 +1216,7 @@
         <v>-21.493816</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-3.546881</v>
+        <v>-2.957588</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>-12.5069</v>
@@ -1268,7 +1268,7 @@
         <v>-0</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.589293</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0</v>
@@ -1864,7 +1864,7 @@
         <v>-21.870375</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.686389</v>
+        <v>-3.097096</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-12.8061</v>
@@ -1968,7 +1968,7 @@
         <v>-21.870375</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.686389</v>
+        <v>-3.097096</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-12.8061</v>
@@ -2102,7 +2102,7 @@
         <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0</v>
+        <v>-19.92478330315108</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0</v>
@@ -6039,7 +6039,7 @@
         <v>0.032332</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.314069</v>
       </c>
       <c r="E107" s="3" t="n">
         <v>0.631138</v>
@@ -6051,7 +6051,7 @@
         <v>0</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="I107" s="3" t="n">
         <v>0.0575</v>
@@ -6228,10 +6228,10 @@
         <v>0</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.018562</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.404142</v>
       </c>
     </row>
     <row r="111">
@@ -16348,7 +16348,11 @@
           <t>Deferred income tax recovery 18</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -16439,7 +16443,11 @@
           <t>Accretion expense 11</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -18907,7 +18915,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -23413,7 +23425,11 @@
           <t>Issuance of broker warrants in private placement (Note 7)</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -23593,7 +23609,11 @@
           <t>Share-based payment expense 6</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -24137,7 +24157,11 @@
           <t>Issuance of broker warrants in private placement (Note 6)</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -26206,7 +26230,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -30944,7 +30972,11 @@
           <t>Share-based payment expenses - - - 314,069</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -31589,7 +31621,11 @@
           <t>Cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -31868,7 +31904,11 @@
           <t>Common Shares Issued for cash</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -32703,7 +32743,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E280" s="5" t="n">
         <v>0.1</v>
       </c>
@@ -33458,7 +33502,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -34397,7 +34445,11 @@
           <t>Deferred income tax recovery 18</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
